--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -10865,7 +10865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10874,12 +10874,13 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -10899,6 +10900,7 @@
       <c r="J1" s="10" t="n"/>
       <c r="K1" s="10" t="n"/>
       <c r="L1" s="10" t="n"/>
+      <c r="M1" s="10" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="13" t="inlineStr">
@@ -10926,27 +10928,32 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>P/B</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>Div %</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>P/S</t>
         </is>
@@ -10976,21 +10983,24 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="I4" s="22" t="n">
         <v>1.337323840582209</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="J4" s="22" t="n">
         <v>0.2358961702739243</v>
       </c>
-      <c r="J4" s="23" t="n">
+      <c r="K4" s="23" t="n">
         <v>2.42</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="L4" s="22" t="n">
         <v>0.19885361</v>
       </c>
     </row>
@@ -11018,21 +11028,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Internet &amp; Direct Marketing Retail</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="I5" s="22" t="n">
         <v>1.2546601832671</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="J5" s="22" t="n">
         <v>0.3895122570757942</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="K5" s="23" t="n">
         <v>2.0299999</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="L5" s="22" t="n">
         <v>0.33442965</v>
       </c>
     </row>
@@ -11060,21 +11075,26 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="I6" s="22" t="n">
         <v>1.224320047113935</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="J6" s="22" t="n">
         <v>0.5975976</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="K6" s="23" t="n">
         <v>6.79</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="L6" s="22" t="n">
         <v>0.6178304</v>
       </c>
     </row>
@@ -11102,23 +11122,28 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Interactive Media &amp; Services</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="I7" s="22" t="n">
         <v>1.213706119342358</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="J7" s="22" t="n">
         <v>0.64855975</v>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="L7" s="22" t="n">
         <v>1.076399494270387</v>
       </c>
     </row>
@@ -11146,21 +11171,26 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="I8" s="22" t="n">
         <v>1.201964122014842</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="J8" s="22" t="n">
         <v>0.63487464</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="K8" s="23" t="n">
         <v>2.4300002</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="L8" s="22" t="n">
         <v>0.30129302</v>
       </c>
     </row>
@@ -11188,21 +11218,26 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="I9" s="22" t="n">
         <v>1.196379645329934</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="J9" s="22" t="n">
         <v>0.3814184820374598</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="K9" s="23" t="n">
         <v>2.77</v>
       </c>
-      <c r="K9" s="22" t="n">
+      <c r="L9" s="22" t="n">
         <v>0.47579452</v>
       </c>
     </row>
@@ -11230,21 +11265,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="I10" s="22" t="n">
         <v>1.19387677304337</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.4305136</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="K10" s="23" t="n">
         <v>3.28</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="L10" s="22" t="n">
         <v>0.3348663</v>
       </c>
     </row>
@@ -11272,21 +11312,26 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="I11" s="22" t="n">
         <v>1.187594330021412</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="J11" s="22" t="n">
         <v>0.82867485</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="K11" s="23" t="n">
         <v>3.55</v>
       </c>
-      <c r="K11" s="22" t="n">
+      <c r="L11" s="22" t="n">
         <v>0.45901608</v>
       </c>
     </row>
@@ -11314,21 +11359,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="I12" s="22" t="n">
         <v>1.172504383176419</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="J12" s="22" t="n">
         <v>0.605814</v>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="K12" s="23" t="n">
         <v>4.21</v>
       </c>
-      <c r="K12" s="22" t="n">
+      <c r="L12" s="22" t="n">
         <v>0.5752</v>
       </c>
     </row>
@@ -11356,21 +11406,24 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="I13" s="22" t="n">
         <v>1.17208086301225</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="J13" s="22" t="n">
         <v>0.3329555299332747</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="K13" s="23" t="n">
         <v>2.21</v>
       </c>
-      <c r="K13" s="22" t="n">
+      <c r="L13" s="22" t="n">
         <v>0.13220902</v>
       </c>
     </row>
@@ -11398,21 +11451,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="I14" s="22" t="n">
         <v>1.168783020601786</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="J14" s="22" t="n">
         <v>0.6870092</v>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="K14" s="23" t="n">
         <v>2.53</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="L14" s="22" t="n">
         <v>0.9294438</v>
       </c>
     </row>
@@ -11440,21 +11498,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>Distributors</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="I15" s="22" t="n">
         <v>1.164103836676694</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="J15" s="22" t="n">
         <v>0.5009125</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="K15" s="23" t="n">
         <v>8.33</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="L15" s="22" t="n">
         <v>1.6125863</v>
       </c>
     </row>
@@ -11482,21 +11545,24 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="I16" s="22" t="n">
         <v>1.163897066936411</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="J16" s="22" t="n">
         <v>0.9925171574056828</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="K16" s="23" t="n">
         <v>4.9200002</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="L16" s="22" t="n">
         <v>1.2269952</v>
       </c>
     </row>
@@ -11524,23 +11590,26 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="I17" s="22" t="n">
         <v>1.152290474548095</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="J17" s="22" t="n">
         <v>0.5449940720767228</v>
       </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="L17" s="22" t="n">
         <v>0.8796080168298662</v>
       </c>
     </row>
@@ -11568,21 +11637,24 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="I18" s="22" t="n">
         <v>1.151619597547656</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="J18" s="22" t="n">
         <v>0.3869141557375681</v>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="K18" s="23" t="n">
         <v>2.79</v>
       </c>
-      <c r="K18" s="22" t="n">
+      <c r="L18" s="22" t="n">
         <v>0.3518272690665361</v>
       </c>
     </row>
@@ -11610,23 +11682,28 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="I19" s="22" t="n">
         <v>1.145311286187199</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="J19" s="22" t="n">
         <v>0.07192945000000001</v>
       </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="L19" s="22" t="n">
         <v>3.837890044653707</v>
       </c>
     </row>
@@ -11654,21 +11731,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="I20" s="22" t="n">
         <v>1.129692505982211</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="J20" s="22" t="n">
         <v>0.3569352</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="K20" s="23" t="n">
         <v>2.02</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="L20" s="22" t="n">
         <v>0.4588686</v>
       </c>
     </row>
@@ -11696,21 +11778,24 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="I21" s="22" t="n">
         <v>1.128749512459602</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="J21" s="22" t="n">
         <v>0.3574623360623071</v>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="K21" s="23" t="n">
         <v>2.0299999</v>
       </c>
-      <c r="K21" s="22" t="n">
+      <c r="L21" s="22" t="n">
         <v>0.20222703</v>
       </c>
     </row>
@@ -11738,23 +11823,26 @@
           <t>Health Care</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="I22" s="22" t="n">
         <v>1.126098255566523</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="J22" s="22" t="n">
         <v>0.4404573070670534</v>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="K22" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="L22" s="22" t="n">
         <v>1.1023238</v>
       </c>
     </row>
@@ -11782,23 +11870,28 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="I23" s="22" t="n">
         <v>1.114077191724072</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="J23" s="22" t="n">
         <v>0.14073937</v>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="K23" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="L23" s="22" t="n">
         <v>0.2087546874822286</v>
       </c>
     </row>
@@ -11826,23 +11919,28 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>Internet &amp; Direct Marketing Retail</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="I24" s="22" t="n">
         <v>1.101049539651115</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="J24" s="22" t="n">
         <v>0.2626032</v>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="K24" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K24" s="22" t="n">
+      <c r="L24" s="22" t="n">
         <v>1.151275859708347</v>
       </c>
     </row>
@@ -11870,21 +11968,26 @@
           <t>Health Care</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H25" s="22" t="n">
+      <c r="I25" s="22" t="n">
         <v>1.09772165902702</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="J25" s="22" t="n">
         <v>0.37324485</v>
       </c>
-      <c r="J25" s="23" t="n">
+      <c r="K25" s="23" t="n">
         <v>6.3</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="L25" s="22" t="n">
         <v>1.126572896664314</v>
       </c>
     </row>
@@ -11912,23 +12015,26 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="I26" s="22" t="n">
         <v>1.09623561521307</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="J26" s="22" t="n">
         <v>1.168593365730836</v>
       </c>
-      <c r="J26" s="25" t="inlineStr">
+      <c r="K26" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K26" s="22" t="n">
+      <c r="L26" s="22" t="n">
         <v>1.8895935</v>
       </c>
     </row>
@@ -11956,21 +12062,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H27" s="22" t="n">
+      <c r="I27" s="22" t="n">
         <v>1.095490665810664</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="J27" s="22" t="n">
         <v>0.2918288</v>
       </c>
-      <c r="J27" s="23" t="n">
+      <c r="K27" s="23" t="n">
         <v>7.0700005</v>
       </c>
-      <c r="K27" s="22" t="n">
+      <c r="L27" s="22" t="n">
         <v>0.38369063</v>
       </c>
     </row>
@@ -11998,21 +12109,24 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="I28" s="22" t="n">
         <v>1.082675977629569</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="J28" s="22" t="n">
         <v>1.0374141</v>
       </c>
-      <c r="J28" s="23" t="n">
+      <c r="K28" s="23" t="n">
         <v>0.5599999999999999</v>
       </c>
-      <c r="K28" s="22" t="n">
+      <c r="L28" s="22" t="n">
         <v>2.9770486</v>
       </c>
     </row>
@@ -12040,23 +12154,28 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H29" s="22" t="n">
+      <c r="I29" s="22" t="n">
         <v>1.081940931362408</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="J29" s="22" t="n">
         <v>0.5689394</v>
       </c>
-      <c r="J29" s="25" t="inlineStr">
+      <c r="K29" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K29" s="22" t="n">
+      <c r="L29" s="22" t="n">
         <v>0.9480809</v>
       </c>
     </row>
@@ -12084,21 +12203,26 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="I30" s="22" t="n">
         <v>1.081044056088647</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="J30" s="22" t="n">
         <v>0.36005497</v>
       </c>
-      <c r="J30" s="23" t="n">
+      <c r="K30" s="23" t="n">
         <v>3.52</v>
       </c>
-      <c r="K30" s="22" t="n">
+      <c r="L30" s="22" t="n">
         <v>0.26927328</v>
       </c>
     </row>
@@ -12126,23 +12250,26 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
+      <c r="G31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H31" s="22" t="n">
+      <c r="I31" s="22" t="n">
         <v>1.077025085586687</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="J31" s="22" t="n">
         <v>0.6557044396837195</v>
       </c>
-      <c r="J31" s="25" t="inlineStr">
+      <c r="K31" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K31" s="22" t="n">
+      <c r="L31" s="22" t="n">
         <v>0.7902293526088751</v>
       </c>
     </row>
@@ -12170,21 +12297,24 @@
           <t>Health Care</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="I32" s="22" t="n">
         <v>1.076618108296869</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="J32" s="22" t="n">
         <v>0.4577384913211642</v>
       </c>
-      <c r="J32" s="23" t="n">
+      <c r="K32" s="23" t="n">
         <v>5.71</v>
       </c>
-      <c r="K32" s="22" t="n">
+      <c r="L32" s="22" t="n">
         <v>0.5612516400000001</v>
       </c>
     </row>
@@ -12210,21 +12340,24 @@
       <c r="F33" s="20" t="n">
         <v/>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="I33" s="22" t="n">
         <v>1.072794052555671</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="J33" s="22" t="n">
         <v>0.57788193</v>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="K33" s="23" t="n">
         <v>1.39</v>
       </c>
-      <c r="K33" s="22" t="n">
+      <c r="L33" s="22" t="n">
         <v>0.50739163</v>
       </c>
     </row>
@@ -12252,21 +12385,24 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="G34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="I34" s="22" t="n">
         <v>1.07027397463544</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="J34" s="22" t="n">
         <v>0.7937623623751395</v>
       </c>
-      <c r="J34" s="23" t="n">
+      <c r="K34" s="23" t="n">
         <v>2.8800001</v>
       </c>
-      <c r="K34" s="22" t="n">
+      <c r="L34" s="22" t="n">
         <v>1.4009893</v>
       </c>
     </row>
@@ -12292,21 +12428,24 @@
       <c r="F35" s="20" t="n">
         <v/>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H35" s="22" t="n">
+      <c r="I35" s="22" t="n">
         <v>1.068682304326143</v>
       </c>
-      <c r="I35" s="22" t="n">
+      <c r="J35" s="22" t="n">
         <v>0.6041536</v>
       </c>
-      <c r="J35" s="23" t="n">
+      <c r="K35" s="23" t="n">
         <v>1.23000005</v>
       </c>
-      <c r="K35" s="22" t="n">
+      <c r="L35" s="22" t="n">
         <v>0.45060313</v>
       </c>
     </row>
@@ -12334,23 +12473,26 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G36" s="24" t="inlineStr">
+      <c r="G36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H36" s="22" t="n">
+      <c r="I36" s="22" t="n">
         <v>1.061212203475943</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="J36" s="22" t="n">
         <v>0.6916597246694085</v>
       </c>
-      <c r="J36" s="25" t="inlineStr">
+      <c r="K36" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K36" s="22" t="n">
+      <c r="L36" s="22" t="n">
         <v>0.23250532</v>
       </c>
     </row>
@@ -12376,21 +12518,24 @@
       <c r="F37" s="20" t="n">
         <v/>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H37" s="22" t="n">
+      <c r="I37" s="22" t="n">
         <v>1.060366004632101</v>
       </c>
-      <c r="I37" s="22" t="n">
+      <c r="J37" s="22" t="n">
         <v>0.809476</v>
       </c>
-      <c r="J37" s="23" t="n">
+      <c r="K37" s="23" t="n">
         <v>4.9200002</v>
       </c>
-      <c r="K37" s="22" t="n">
+      <c r="L37" s="22" t="n">
         <v>1.9716996</v>
       </c>
     </row>
@@ -12418,21 +12563,26 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G38" s="24" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H38" s="22" t="n">
+      <c r="I38" s="22" t="n">
         <v>1.05043788016529</v>
       </c>
-      <c r="I38" s="22" t="n">
+      <c r="J38" s="22" t="n">
         <v>0.7234581</v>
       </c>
-      <c r="J38" s="23" t="n">
+      <c r="K38" s="23" t="n">
         <v>7.27</v>
       </c>
-      <c r="K38" s="22" t="n">
+      <c r="L38" s="22" t="n">
         <v>1.872427</v>
       </c>
     </row>
@@ -12460,21 +12610,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>Hotels, Restaurants &amp; Leisure</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
         <is>
           <t>YELLOW</t>
         </is>
       </c>
-      <c r="H39" s="22" t="n">
+      <c r="I39" s="22" t="n">
         <v>1.048092762427114</v>
       </c>
-      <c r="I39" s="22" t="n">
+      <c r="J39" s="22" t="n">
         <v>0.65109336</v>
       </c>
-      <c r="J39" s="23" t="n">
+      <c r="K39" s="23" t="n">
         <v>9.379999999999999</v>
       </c>
-      <c r="K39" s="22" t="n">
+      <c r="L39" s="22" t="n">
         <v>0.49421084</v>
       </c>
     </row>
@@ -12502,21 +12657,26 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H40" s="22" t="n">
+      <c r="I40" s="22" t="n">
         <v>1.036756677485999</v>
       </c>
-      <c r="I40" s="22" t="n">
+      <c r="J40" s="22" t="n">
         <v>0.43636367</v>
       </c>
-      <c r="J40" s="23" t="n">
+      <c r="K40" s="23" t="n">
         <v>5.6500003</v>
       </c>
-      <c r="K40" s="22" t="n">
+      <c r="L40" s="22" t="n">
         <v>0.20419927</v>
       </c>
     </row>
@@ -12544,21 +12704,24 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G41" s="24" t="inlineStr">
+      <c r="G41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H41" s="22" t="n">
+      <c r="I41" s="22" t="n">
         <v>1.030492076157528</v>
       </c>
-      <c r="I41" s="22" t="n">
+      <c r="J41" s="22" t="n">
         <v>0.4894186186926682</v>
       </c>
-      <c r="J41" s="23" t="n">
+      <c r="K41" s="23" t="n">
         <v>6.1100002</v>
       </c>
-      <c r="K41" s="22" t="n">
+      <c r="L41" s="22" t="n">
         <v>0.3481376</v>
       </c>
     </row>
@@ -12586,23 +12749,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="G42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H42" s="22" t="n">
+      <c r="I42" s="22" t="n">
         <v>1.028169691118431</v>
       </c>
-      <c r="I42" s="22" t="n">
+      <c r="J42" s="22" t="n">
         <v>0.7820751288732902</v>
       </c>
-      <c r="J42" s="25" t="inlineStr">
+      <c r="K42" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K42" s="22" t="n">
+      <c r="L42" s="22" t="n">
         <v>0.160262220867965</v>
       </c>
     </row>
@@ -12630,23 +12796,28 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="G43" s="24" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>Independent Power and Renewable Electricity Producers</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H43" s="22" t="n">
+      <c r="I43" s="22" t="n">
         <v>1.024547950517395</v>
       </c>
-      <c r="I43" s="22" t="n">
+      <c r="J43" s="22" t="n">
         <v>0.14083</v>
       </c>
-      <c r="J43" s="25" t="inlineStr">
+      <c r="K43" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K43" s="22" t="n">
+      <c r="L43" s="22" t="n">
         <v>0.9045904154520544</v>
       </c>
     </row>
@@ -12674,21 +12845,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="H44" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H44" s="22" t="n">
+      <c r="I44" s="22" t="n">
         <v>1.021613930857689</v>
       </c>
-      <c r="I44" s="22" t="n">
+      <c r="J44" s="22" t="n">
         <v>0.8297809</v>
       </c>
-      <c r="J44" s="23" t="n">
+      <c r="K44" s="23" t="n">
         <v>5.35</v>
       </c>
-      <c r="K44" s="22" t="n">
+      <c r="L44" s="22" t="n">
         <v>0.7334186</v>
       </c>
     </row>
@@ -12716,21 +12892,24 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G45" s="24" t="inlineStr">
+      <c r="G45" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H45" s="22" t="n">
+      <c r="I45" s="22" t="n">
         <v>1.019384927967752</v>
       </c>
-      <c r="I45" s="22" t="n">
+      <c r="J45" s="22" t="n">
         <v>0.6199516180391726</v>
       </c>
-      <c r="J45" s="23" t="n">
+      <c r="K45" s="23" t="n">
         <v>4.3</v>
       </c>
-      <c r="K45" s="22" t="n">
+      <c r="L45" s="22" t="n">
         <v>2.2647114</v>
       </c>
     </row>
@@ -12758,21 +12937,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H46" s="22" t="n">
+      <c r="I46" s="22" t="n">
         <v>1.019209861728622</v>
       </c>
-      <c r="I46" s="22" t="n">
+      <c r="J46" s="22" t="n">
         <v>0.41230643</v>
       </c>
-      <c r="J46" s="23" t="n">
+      <c r="K46" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="K46" s="22" t="n">
+      <c r="L46" s="22" t="n">
         <v>0.483827</v>
       </c>
     </row>
@@ -12800,23 +12984,26 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="G47" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H47" s="22" t="n">
+      <c r="I47" s="22" t="n">
         <v>1.015941915770137</v>
       </c>
-      <c r="I47" s="22" t="n">
+      <c r="J47" s="22" t="n">
         <v>0.183928423362757</v>
       </c>
-      <c r="J47" s="25" t="inlineStr">
+      <c r="K47" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K47" s="22" t="n">
+      <c r="L47" s="22" t="n">
         <v>0.6088967</v>
       </c>
     </row>
@@ -12844,21 +13031,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G48" s="21" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>Distributors</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H48" s="22" t="n">
+      <c r="I48" s="22" t="n">
         <v>1.015602077566072</v>
       </c>
-      <c r="I48" s="22" t="n">
+      <c r="J48" s="22" t="n">
         <v>0.4591028</v>
       </c>
-      <c r="J48" s="23" t="n">
+      <c r="K48" s="23" t="n">
         <v>1.72</v>
       </c>
-      <c r="K48" s="22" t="n">
+      <c r="L48" s="22" t="n">
         <v>0.5316604</v>
       </c>
     </row>
@@ -12886,21 +13078,24 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G49" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="H49" s="22" t="n">
+      <c r="I49" s="22" t="n">
         <v>1.012591896435186</v>
       </c>
-      <c r="I49" s="22" t="n">
+      <c r="J49" s="22" t="n">
         <v>0.4951807783269601</v>
       </c>
-      <c r="J49" s="23" t="n">
+      <c r="K49" s="23" t="n">
         <v>5.11</v>
       </c>
-      <c r="K49" s="22" t="n">
+      <c r="L49" s="22" t="n">
         <v>0.45824897</v>
       </c>
     </row>
@@ -12928,21 +13123,26 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G50" s="24" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>Construction &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H50" s="22" t="n">
+      <c r="I50" s="22" t="n">
         <v>1.01079422535051</v>
       </c>
-      <c r="I50" s="22" t="n">
+      <c r="J50" s="22" t="n">
         <v>0.7220866</v>
       </c>
-      <c r="J50" s="23" t="n">
+      <c r="K50" s="23" t="n">
         <v>4.0700004</v>
       </c>
-      <c r="K50" s="22" t="n">
+      <c r="L50" s="22" t="n">
         <v>0.46383998</v>
       </c>
     </row>
@@ -12970,23 +13170,26 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="G51" s="24" t="inlineStr">
+      <c r="G51" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H51" s="22" t="n">
+      <c r="I51" s="22" t="n">
         <v>1.010714964634912</v>
       </c>
-      <c r="I51" s="22" t="n">
+      <c r="J51" s="22" t="n">
         <v>0.6170253471017332</v>
       </c>
-      <c r="J51" s="25" t="inlineStr">
+      <c r="K51" s="25" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K51" s="22" t="n">
+      <c r="L51" s="22" t="n">
         <v>0.22095597</v>
       </c>
     </row>
@@ -13014,21 +13217,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G52" s="24" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>Textiles, Apparel &amp; Luxury Goods</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H52" s="22" t="n">
+      <c r="I52" s="22" t="n">
         <v>1.01049253958095</v>
       </c>
-      <c r="I52" s="22" t="n">
+      <c r="J52" s="22" t="n">
         <v>0.3580247</v>
       </c>
-      <c r="J52" s="23" t="n">
+      <c r="K52" s="23" t="n">
         <v>9.34</v>
       </c>
-      <c r="K52" s="22" t="n">
+      <c r="L52" s="22" t="n">
         <v>0.3563411</v>
       </c>
     </row>
@@ -13056,27 +13264,32 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="G53" s="24" t="inlineStr">
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H53" s="22" t="n">
+      <c r="I53" s="22" t="n">
         <v>1.008526545885407</v>
       </c>
-      <c r="I53" s="22" t="n">
+      <c r="J53" s="22" t="n">
         <v>0.7311028000000001</v>
       </c>
-      <c r="J53" s="23" t="n">
+      <c r="K53" s="23" t="n">
         <v>3.39</v>
       </c>
-      <c r="K53" s="22" t="n">
+      <c r="L53" s="22" t="n">
         <v>1.4634235</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
@@ -26185,10 +26398,10 @@
         <v>10</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="34" t="n">
         <v>0</v>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -18347,7 +18347,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -25,14 +25,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_264450_KQ" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_120240_KQ" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_052330_KQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_1V5_F" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_1900_HK" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_6155_T" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_031510_KQ" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_035610_KQ" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1900_HK" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_2348_HK" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_219420_KQ" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_6907_T" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_2348_HK" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_219420_KQ" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_6907_T" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_1V5_F" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_0057_HK" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_7877_T" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_SHRIDINE_BO" sheetId="29" state="visible" r:id="rId29"/>
@@ -45,16 +45,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_3908_T" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_051160_KQ" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_LSIP_JK" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_2101_HK" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_SPG_BK" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_0114_HK" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_1118_HK" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_1118_HK" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_2101_HK" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_SPG_BK" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_0114_HK" sheetId="42" state="visible" r:id="rId42"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_1905_T" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_053980_KQ" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_7722_T" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_088130_KQ" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_131090_KQ" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_1281_HK" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_1281_HK" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_053980_KQ" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_7722_T" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_088130_KQ" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_131090_KQ" sheetId="48" state="visible" r:id="rId48"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_0725_HK" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_1798_T" sheetId="50" state="visible" r:id="rId50"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_052790_KQ" sheetId="51" state="visible" r:id="rId51"/>
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>26,398</t>
+          <t>28,051</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,997</t>
+          <t>27,649</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1.5% of universe</t>
+          <t>1.4% of universe</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 26,398 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 28,051 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -4625,10 +4625,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>2.36836202849494</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -5120,7 +5118,7 @@
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>1.926120339523525</v>
+        <v>2.293524826119498</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -5335,7 +5333,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#16    1V5.F    Zaklady Azotowe Pulawy S.A.</t>
+          <t>#16    1900.HK    China ITS (Holdings) Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5362,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.145311286187199</v>
+        <v>1.13653565357367</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -5382,7 +5380,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5392,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5404,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>IT Services</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5416,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5427,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>228294787.022644</v>
+        <v>38413174.78646944</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -5439,7 +5437,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>59484452.22933506</v>
+        <v>184011076.58835</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -5485,7 +5483,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6586837220672349</v>
+        <v>0.6569190529874979</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -5493,7 +5491,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7014089319704393</v>
+        <v>0.771852126</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -5503,7 +5501,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5869928030279979</v>
+        <v>0.5610054348313883</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -5521,7 +5519,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -5539,7 +5537,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.8433652825604028</v>
+        <v>0.9112208468856676</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -5547,7 +5545,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.198</v>
+        <v>1.1534</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -5557,7 +5555,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.6549592322937731</v>
+        <v>0.5689519512401612</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -5565,7 +5563,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -5582,7 +5580,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.07192945000000001</v>
+        <v>0.14073937</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -5602,7 +5600,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>18.81984303849444</v>
+        <v>-1.481561709816219</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -5610,7 +5608,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-1.270812315309707</v>
+        <v>-3.295933190758246</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -5619,10 +5617,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>2.717728292461044</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -5630,7 +5626,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>-5.85163945049248</v>
+        <v>10.50588238891964</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -5650,7 +5646,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>20.39278455619219</v>
+        <v>15.30627925009698</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -5660,7 +5656,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>3.837890044653707</v>
+        <v>0.2087546874822286</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5664,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>95.975995</v>
+        <v>45.372</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -5700,7 +5696,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>87.2456000630648</v>
+        <v>208.630840965565</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -5708,7 +5704,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>13.00334076107754</v>
+        <v>13.18171671421966</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5718,7 +5714,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>21.94434020049347</v>
+        <v>3.123799128486372</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -5726,7 +5722,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>1.42</v>
+        <v>-50.43</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -5746,21 +5742,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.07)</t>
+          <t>·  Sub-book  (P/B 0.14)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (96% insider)</t>
+          <t>·  Insider-aligned  (45% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -7243,10 +7239,8 @@
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E30" s="23" t="n">
+        <v>109.0788531454151</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -7439,492 +7433,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#20    1900.HK    China ITS (Holdings) Co., Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.114077191724072</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Nano Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>38413174.78646944</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>184011076.58835</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.6439380334801871</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.771852126</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5610054348313883</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7391304347826086</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.9112208468856676</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.1534</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.5689519512401612</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.14073937</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>-1.481561709816219</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-3.295933190758246</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>2.717728292461044</v>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>10.50588238891964</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>15.30627925009698</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>0.2087546874822286</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>45.372</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>208.630840965565</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>13.18171671421966</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>3.123799128486372</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>-50.43</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (45% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 20 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7939,7 +7447,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#21    2348.HK    Dawnrays Pharmaceutical (Holdings) Limited</t>
+          <t>#20    2348.HK    Dawnrays Pharmaceutical (Holdings) Limited</t>
         </is>
       </c>
     </row>
@@ -8387,7 +7895,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 21 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 20 of 50</t>
         </is>
       </c>
     </row>
@@ -8416,7 +7924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -8437,7 +7945,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#22    219420.KQ    Linkgenesis Co., Ltd.</t>
+          <t>#21    219420.KQ    Linkgenesis Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8377,7 @@
     <row r="48">
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 22 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 21 of 50</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -8917,7 +8425,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#23    6907.T    GEOMATEC Co., Ltd.</t>
+          <t>#22    6907.T    GEOMATEC Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -9358,7 +8866,7 @@
     <row r="49">
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 23 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 22 of 50</t>
         </is>
       </c>
     </row>
@@ -9374,6 +8882,494 @@
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="B43:E45"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#23    1V5.F    Zaklady Azotowe Pulawy S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.087720636570767</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>228294787.022644</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>59484452.22933506</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6255625750890143</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.7014089319704393</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5869928030279979</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.8433652825604028</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.198</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.6549592322937731</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.07192945000000001</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>18.81984303849444</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-1.270812315309707</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>-5.85163945049248</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>20.39278455619219</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>3.837890044653707</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>95.975995</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>87.2456000630648</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>13.00334076107754</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>21.94434020049347</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (96% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 23 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -10466,8 +10462,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Manufacturing - Textiles</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -11672,27 +11670,27 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>1V5.F</t>
+          <t>1900.HK</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Zaklady Azotowe Pulawy S.A.</t>
+          <t>China ITS (Holdings) Co., Ltd.</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -11701,10 +11699,10 @@
         </is>
       </c>
       <c r="I19" s="22" t="n">
-        <v>1.145311286187199</v>
+        <v>1.13653565357367</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>0.07192945000000001</v>
+        <v>0.14073937</v>
       </c>
       <c r="K19" s="25" t="inlineStr">
         <is>
@@ -11712,7 +11710,7 @@
         </is>
       </c>
       <c r="L19" s="22" t="n">
-        <v>3.837890044653707</v>
+        <v>0.2087546874822286</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -11860,12 +11858,12 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>1900.HK</t>
+          <t>2348.HK</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>China ITS (Holdings) Co., Ltd.</t>
+          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -11875,12 +11873,12 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -11889,18 +11887,16 @@
         </is>
       </c>
       <c r="I23" s="22" t="n">
-        <v>1.114077191724072</v>
+        <v>1.09772165902702</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>0.14073937</v>
-      </c>
-      <c r="K23" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.37324485</v>
+      </c>
+      <c r="K23" s="23" t="n">
+        <v>6.3</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>0.2087546874822286</v>
+        <v>1.126572896664314</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -11909,45 +11905,45 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>2348.HK</t>
+          <t>219420.KQ</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
+          <t>Linkgenesis Co., Ltd.</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="I24" s="22" t="n">
-        <v>1.09772165902702</v>
+        <v>1.09623561521307</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>0.37324485</v>
-      </c>
-      <c r="K24" s="23" t="n">
-        <v>6.3</v>
+        <v>1.168593365730836</v>
+      </c>
+      <c r="K24" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L24" s="22" t="n">
-        <v>1.126572896664314</v>
+        <v>1.8895935</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -11956,17 +11952,17 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>219420.KQ</t>
+          <t>6907.T</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Linkgenesis Co., Ltd.</t>
+          <t>GEOMATEC Co., Ltd.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -11974,8 +11970,10 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G25" s="20" t="n">
-        <v/>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
+        </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
@@ -11983,10 +11981,10 @@
         </is>
       </c>
       <c r="I25" s="22" t="n">
-        <v>1.09623561521307</v>
+        <v>1.09088259195218</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>1.168593365730836</v>
+        <v>0.5689394</v>
       </c>
       <c r="K25" s="25" t="inlineStr">
         <is>
@@ -11994,7 +11992,7 @@
         </is>
       </c>
       <c r="L25" s="22" t="n">
-        <v>1.8895935</v>
+        <v>0.9480809</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -12003,39 +12001,39 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>6907.T</t>
+          <t>1V5.F</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>GEOMATEC Co., Ltd.</t>
+          <t>Zaklady Azotowe Pulawy S.A.</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I26" s="22" t="n">
-        <v>1.09088259195218</v>
+        <v>1.087720636570767</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>0.5689394</v>
+        <v>0.07192945000000001</v>
       </c>
       <c r="K26" s="25" t="inlineStr">
         <is>
@@ -12043,7 +12041,7 @@
         </is>
       </c>
       <c r="L26" s="22" t="n">
-        <v>0.9480809</v>
+        <v>3.837890044653707</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -12164,8 +12162,10 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="G29" s="20" t="n">
-        <v/>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>Manufacturing - Textiles</t>
+        </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
@@ -12204,11 +12204,15 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="F30" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v/>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Containers</t>
+        </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
@@ -12252,8 +12256,10 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="G31" s="20" t="n">
-        <v/>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>Software - Application</t>
+        </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
@@ -12339,11 +12345,15 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="F33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v/>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>Household &amp; Personal Products</t>
+        </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
@@ -12568,11 +12578,15 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="F38" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v/>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>Agricultural Farm Products</t>
+        </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
@@ -12598,12 +12612,12 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>2101.HK</t>
+          <t>1118.HK</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
         <is>
-          <t>Fulu Holdings Limited</t>
+          <t>Golik Holdings Limited</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
@@ -12613,32 +12627,30 @@
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>Internet &amp; Direct Marketing Retail</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="I39" s="22" t="n">
-        <v>1.056414808839897</v>
+        <v>1.057656450375706</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>0.2626032</v>
-      </c>
-      <c r="K39" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.43636367</v>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v>5.6500003</v>
       </c>
       <c r="L39" s="22" t="n">
-        <v>1.151275859708347</v>
+        <v>0.20419927</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -12647,27 +12659,27 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>SPG.BK</t>
+          <t>2101.HK</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>Siam Pan Group Public Company Limited</t>
+          <t>Fulu Holdings Limited</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Internet &amp; Direct Marketing Retail</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12676,16 +12688,18 @@
         </is>
       </c>
       <c r="I40" s="22" t="n">
-        <v>1.05043788016529</v>
+        <v>1.056414808839897</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>0.7234581</v>
-      </c>
-      <c r="K40" s="23" t="n">
-        <v>7.27</v>
+        <v>0.2626032</v>
+      </c>
+      <c r="K40" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L40" s="22" t="n">
-        <v>1.872427</v>
+        <v>1.151275859708347</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -12694,45 +12708,45 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>0114.HK</t>
+          <t>SPG.BK</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
         <is>
-          <t>Herald Holdings Limited</t>
+          <t>Siam Pan Group Public Company Limited</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>Hotels, Restaurants &amp; Leisure</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I41" s="22" t="n">
-        <v>1.048092762427114</v>
+        <v>1.05043788016529</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>0.65109336</v>
+        <v>0.7234581</v>
       </c>
       <c r="K41" s="23" t="n">
-        <v>9.379999999999999</v>
+        <v>7.27</v>
       </c>
       <c r="L41" s="22" t="n">
-        <v>0.49421084</v>
+        <v>1.872427</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -12741,12 +12755,12 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>1118.HK</t>
+          <t>0114.HK</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>Golik Holdings Limited</t>
+          <t>Herald Holdings Limited</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -12756,30 +12770,30 @@
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Hotels, Restaurants &amp; Leisure</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="I42" s="22" t="n">
-        <v>1.036756677485999</v>
+        <v>1.048092762427114</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>0.43636367</v>
+        <v>0.65109336</v>
       </c>
       <c r="K42" s="23" t="n">
-        <v>5.6500003</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="L42" s="22" t="n">
-        <v>0.20419927</v>
+        <v>0.49421084</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -12817,7 +12831,7 @@
         </is>
       </c>
       <c r="I43" s="22" t="n">
-        <v>1.031940548056587</v>
+        <v>1.034308936199668</v>
       </c>
       <c r="J43" s="22" t="n">
         <v>0.7220866</v>
@@ -12835,26 +12849,28 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>053980.KQ</t>
+          <t>1281.HK</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>Osangjaiel Co., Ltd.</t>
+          <t>LongiTech Smart Energy Holding Limited</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v/>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>Independent Power and Renewable Electricity Producers</t>
+        </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
         <is>
@@ -12862,16 +12878,18 @@
         </is>
       </c>
       <c r="I44" s="22" t="n">
-        <v>1.030492076157528</v>
+        <v>1.033435424064562</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>0.4894186186926682</v>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v>6.1100002</v>
+        <v>0.14083</v>
+      </c>
+      <c r="K44" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>0.3481376</v>
+        <v>0.9045904154520544</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -12880,45 +12898,43 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>7722.T</t>
+          <t>053980.KQ</t>
         </is>
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>Kokusai Co., Ltd.</t>
+          <t>Osangjaiel Co., Ltd.</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
-      </c>
-      <c r="H45" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="I45" s="22" t="n">
-        <v>1.02978684230455</v>
+        <v>1.030492076157528</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>0.8297809</v>
+        <v>0.4894186186926682</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>5.35</v>
+        <v>6.1100002</v>
       </c>
       <c r="L45" s="22" t="n">
-        <v>0.7334186</v>
+        <v>0.3481376</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -12927,17 +12943,17 @@
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>088130.KQ</t>
+          <t>7722.T</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>Dong A Eltek Co., Ltd.</t>
+          <t>Kokusai Co., Ltd.</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
@@ -12945,27 +12961,27 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="G46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="I46" s="22" t="n">
-        <v>1.028169691118431</v>
+        <v>1.02978684230455</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>0.7820751288732902</v>
-      </c>
-      <c r="K46" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.8297809</v>
+      </c>
+      <c r="K46" s="23" t="n">
+        <v>5.35</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>0.160262220867965</v>
+        <v>0.7334186</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -12974,12 +12990,12 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>131090.KQ</t>
+          <t>088130.KQ</t>
         </is>
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>Secuve Co., Ltd.</t>
+          <t>Dong A Eltek Co., Ltd.</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -12989,7 +13005,7 @@
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G47" s="20" t="n">
@@ -13001,16 +13017,18 @@
         </is>
       </c>
       <c r="I47" s="22" t="n">
-        <v>1.027540007391494</v>
+        <v>1.028169691118431</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>0.6199516180391726</v>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v>4.3</v>
+        <v>0.7820751288732902</v>
+      </c>
+      <c r="K47" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L47" s="22" t="n">
-        <v>2.2647114</v>
+        <v>0.160262220867965</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -13019,27 +13037,27 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>1281.HK</t>
+          <t>131090.KQ</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>LongiTech Smart Energy Holding Limited</t>
+          <t>Secuve Co., Ltd.</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G48" s="20" t="inlineStr">
         <is>
-          <t>Independent Power and Renewable Electricity Producers</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -13048,18 +13066,16 @@
         </is>
       </c>
       <c r="I48" s="22" t="n">
-        <v>1.024547950517395</v>
+        <v>1.027540007391494</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>0.14083</v>
-      </c>
-      <c r="K48" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.6199516180391726</v>
+      </c>
+      <c r="K48" s="23" t="n">
+        <v>4.3</v>
       </c>
       <c r="L48" s="22" t="n">
-        <v>0.9045904154520544</v>
+        <v>2.2647114</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -13433,8 +13449,10 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
-        <v/>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -13443,8 +13461,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Packaging &amp; Containers</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -13941,8 +13961,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Software - Application</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -14903,8 +14925,10 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
-        <v/>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -14913,8 +14937,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Household &amp; Personal Products</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -17335,8 +17361,10 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
-        <v/>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -17345,8 +17373,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Agricultural Farm Products</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -17750,7 +17780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -17764,7 +17794,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#36    2101.HK    Fulu Holdings Limited</t>
+          <t>#36    1118.HK    Golik Holdings Limited</t>
         </is>
       </c>
     </row>
@@ -17782,9 +17812,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -17793,7 +17823,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.056414808839897</v>
+        <v>1.057656450375706</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -17823,7 +17853,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17865,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Internet &amp; Direct Marketing Retail</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -17847,7 +17877,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17888,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>48701579.34159086</v>
+        <v>87952045.37611957</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17868,7 +17898,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>42302267.46344566</v>
+        <v>461430088.9879612</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -17879,7 +17909,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17923,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Golik Holdings - HK steel wire processor; 2024 rev -17% BUT earnings +14% on margin improvement; P/B 0.45</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17944,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6425515896737461</v>
+        <v>0.6202523288817703</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -17922,7 +17952,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6392964091453174</v>
+        <v>0.5418208434506239</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -17932,7 +17962,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5367343090099357</v>
+        <v>0.5001268369282377</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -17940,7 +17970,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -17968,7 +17998,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.9224527633741668</v>
+        <v>0.703009</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -17976,7 +18006,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.1834</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -17986,7 +18016,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4117110097619753</v>
+        <v>0.5801396844143416</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -17994,7 +18024,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -18011,17 +18041,15 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.2626032</v>
+        <v>0.43636367</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="23" t="n">
+        <v>148.5136648791388</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -18031,7 +18059,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-4.345596984910629</v>
+        <v>2.094</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -18039,7 +18067,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-10.50781641615016</v>
+        <v>-1.467203587166602</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -18049,7 +18077,7 @@
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>-2.998632121052401</v>
+        <v>2.608781354643094</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -18057,7 +18085,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>8.27556220606108</v>
+        <v>17.64657990370041</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -18067,7 +18095,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>16.28802936107025</v>
+        <v>4.615385</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -18075,7 +18103,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>18.68281181082135</v>
+        <v>8.942672594618099</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -18085,7 +18113,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.151275859708347</v>
+        <v>0.20419927</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -18093,7 +18121,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>64.995</v>
+        <v>63.651</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -18102,8 +18130,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
-        <v>79.96849146792644</v>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -18123,7 +18153,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>141.2029637404359</v>
+        <v>68.83632524543646</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -18131,7 +18161,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>-8.011895828121959</v>
+        <v>4.94241658792309</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18141,7 +18171,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>4.394599443190819</v>
+        <v>1.301128022857525</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -18149,7 +18179,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-7.56</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -18169,50 +18199,60 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.26)</t>
+          <t>·  Sub-book  (P/B 0.44)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (65% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
+          <t>·  Insider-aligned  (64% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.7x); cash 120% of mcap; cash &gt; EV (1.30x, net cash 29% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 36 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -18736,6 +18776,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#37    2101.HK    Fulu Holdings Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.056414808839897</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Internet &amp; Direct Marketing Retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>48701579.34159086</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>42302267.46344566</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6425515896737461</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.6392964091453174</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5367343090099357</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.9224527633741668</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.1834</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.4117110097619753</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.2626032</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>-4.345596984910629</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-10.50781641615016</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>-2.998632121052401</v>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>8.27556220606108</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>16.28802936107025</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>18.68281181082135</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>1.151275859708347</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>64.995</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>79.96849146792644</v>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>141.2029637404359</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>-8.011895828121959</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>4.394599443190819</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>-7.56</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (65% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 37 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18750,7 +19272,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#37    SPG.BK    Siam Pan Group Public Company Limited</t>
+          <t>#38    SPG.BK    Siam Pan Group Public Company Limited</t>
         </is>
       </c>
     </row>
@@ -19186,7 +19708,7 @@
     <row r="48">
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 37 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 38 of 50</t>
         </is>
       </c>
     </row>
@@ -19213,7 +19735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -19234,7 +19756,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#38    0114.HK    Herald Holdings Limited</t>
+          <t>#39    0114.HK    Herald Holdings Limited</t>
         </is>
       </c>
     </row>
@@ -19684,7 +20206,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 38 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 39 of 50</t>
         </is>
       </c>
     </row>
@@ -19705,498 +20227,6 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#39    1118.HK    Golik Holdings Limited</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.036756677485999</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Metals &amp; Mining</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>87952045.37611957</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>461430088.9879612</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Golik Holdings - HK steel wire processor; 2024 rev -17% BUT earnings +14% on margin improvement; P/B 0.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.6079958605329637</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.5418208434506239</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5001268369282377</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7391304347826086</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.703009</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.5801396844143416</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.43636367</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>148.5136648791388</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>2.094</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-1.467203587166602</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>2.608781354643094</v>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>17.64657990370041</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>4.615385</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>8.942672594618099</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>0.20419927</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>63.651</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>68.83632524543646</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>4.94241658792309</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>1.301128022857525</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>15.73</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (64% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.7x); cash 120% of mcap; cash &gt; EV (1.30x, net cash 29% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 39 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -20255,7 +20285,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.031940548056587</v>
+        <v>1.034308936199668</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -20438,7 +20468,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.22</v>
+        <v>1.2228</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -20508,10 +20538,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>2.822578727694324</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -20704,6 +20732,490 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#41    1281.HK    LongiTech Smart Energy Holding Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.033435424064562</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Independent Power and Renewable Electricity Producers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>17428710.39306092</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>19266963.3630279</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6291497860677019</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.6626164776618847</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5145782893017455</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.8794749681014746</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.1628</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.4655292998699878</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.14083</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>-3.322634386904862</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-7.396120066301267</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>2.15667527759927</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>7.585980566515093</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>31.31714285714285</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>0.9045904154520544</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>65.373003</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>99.15826792971392</v>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>181.9727797636792</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>22.5586749656398</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>1.54376636882513</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>-24.14</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (65% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 41 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20718,7 +21230,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#41    053980.KQ    Osangjaiel Co., Ltd.</t>
+          <t>#42    053980.KQ    Osangjaiel Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21671,7 @@
     <row r="49">
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 41 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 42 of 50</t>
         </is>
       </c>
     </row>
@@ -21187,7 +21699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -21208,7 +21720,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#42    7722.T    Kokusai Co., Ltd.</t>
+          <t>#43    7722.T    Kokusai Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -21656,7 +22168,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 42 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 43 of 50</t>
         </is>
       </c>
     </row>
@@ -21685,7 +22197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -21706,7 +22218,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#43    088130.KQ    Dong A Eltek Co., Ltd.</t>
+          <t>#44    088130.KQ    Dong A Eltek Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -22146,7 +22658,7 @@
     <row r="48">
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 43 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 44 of 50</t>
         </is>
       </c>
     </row>
@@ -22173,7 +22685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -22194,7 +22706,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#44    131090.KQ    Secuve Co., Ltd.</t>
+          <t>#45    131090.KQ    Secuve Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -22263,8 +22775,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -22637,7 +23151,7 @@
     <row r="49">
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 44 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 45 of 50</t>
         </is>
       </c>
     </row>
@@ -22653,490 +23167,6 @@
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#45    1281.HK    LongiTech Smart Energy Holding Limited</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.024547950517395</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Independent Power and Renewable Electricity Producers</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Nano Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>17428710.39306092</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>19266963.3630279</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.6291497860677019</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.6626164776618847</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5145782893017455</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.8794749681014746</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.1528</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.4655292998699878</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.14083</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>-3.322634386904862</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-7.396120066301267</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>2.15667527759927</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>7.585980566515093</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>31.31714285714285</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>0.9045904154520544</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>65.373003</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>99.15826792971392</v>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>181.9727797636792</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>22.5586749656398</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>1.54376636882513</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>-24.14</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (65% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 45 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -25906,10 +25936,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>3.453619312275121</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -26180,22 +26208,22 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>26398</v>
+        <v>28051</v>
       </c>
       <c r="D5" s="31" t="n">
         <v>122</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>99</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25997</v>
+        <v>27649</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.519054473823775</v>
+        <v>1.433103989162597</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -26442,7 +26470,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="34" t="n">
         <v>0</v>
@@ -26451,10 +26479,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
